--- a/output/yearly_population_iteration_95_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_95_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7264</v>
+        <v>7751</v>
       </c>
       <c r="C2" t="n">
-        <v>3838</v>
+        <v>5261</v>
       </c>
       <c r="D2" t="n">
-        <v>38877</v>
+        <v>25511</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4718</v>
+        <v>4037</v>
       </c>
       <c r="C3" t="n">
-        <v>5201</v>
+        <v>3700</v>
       </c>
       <c r="D3" t="n">
-        <v>17430</v>
+        <v>12291</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3606</v>
+        <v>2737</v>
       </c>
       <c r="C4" t="n">
-        <v>4896</v>
+        <v>4258</v>
       </c>
       <c r="D4" t="n">
-        <v>7780</v>
+        <v>5557</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2107</v>
+        <v>1747</v>
       </c>
       <c r="C5" t="n">
-        <v>3636</v>
+        <v>4004</v>
       </c>
       <c r="D5" t="n">
-        <v>2925</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1113</v>
+        <v>1038</v>
       </c>
       <c r="C6" t="n">
-        <v>2061</v>
+        <v>3296</v>
       </c>
       <c r="D6" t="n">
-        <v>1220</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>536</v>
+        <v>507</v>
       </c>
       <c r="C7" t="n">
-        <v>1189</v>
+        <v>2068</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="C8" t="n">
-        <v>583</v>
+        <v>936</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>291</v>
+        <v>369</v>
       </c>
       <c r="D9" t="n">
         <v>310</v>
@@ -895,10 +895,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7988</v>
+        <v>7313</v>
       </c>
       <c r="C2" t="n">
-        <v>5789</v>
+        <v>11250</v>
       </c>
       <c r="D2" t="n">
-        <v>43925</v>
+        <v>25028</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4830</v>
+        <v>4599</v>
       </c>
       <c r="C3" t="n">
-        <v>4012</v>
+        <v>3886</v>
       </c>
       <c r="D3" t="n">
-        <v>19175</v>
+        <v>13262</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3500</v>
+        <v>2820</v>
       </c>
       <c r="C4" t="n">
-        <v>4943</v>
+        <v>3896</v>
       </c>
       <c r="D4" t="n">
-        <v>9043</v>
+        <v>6433</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2427</v>
+        <v>1924</v>
       </c>
       <c r="C5" t="n">
-        <v>4118</v>
+        <v>4001</v>
       </c>
       <c r="D5" t="n">
-        <v>3628</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1416</v>
+        <v>1240</v>
       </c>
       <c r="C6" t="n">
-        <v>2766</v>
+        <v>3589</v>
       </c>
       <c r="D6" t="n">
-        <v>1453</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>702</v>
+        <v>659</v>
       </c>
       <c r="C7" t="n">
-        <v>1569</v>
+        <v>2600</v>
       </c>
       <c r="D7" t="n">
-        <v>740</v>
+        <v>715</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="C8" t="n">
-        <v>850</v>
+        <v>1434</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C9" t="n">
-        <v>411</v>
+        <v>604</v>
       </c>
       <c r="D9" t="n">
         <v>325</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>241</v>
+        <v>277</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9438</v>
+        <v>9106</v>
       </c>
       <c r="C2" t="n">
-        <v>6755</v>
+        <v>11321</v>
       </c>
       <c r="D2" t="n">
-        <v>44521</v>
+        <v>22019</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5002</v>
+        <v>4671</v>
       </c>
       <c r="C3" t="n">
-        <v>4217</v>
+        <v>6244</v>
       </c>
       <c r="D3" t="n">
-        <v>21085</v>
+        <v>13898</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3453</v>
+        <v>3041</v>
       </c>
       <c r="C4" t="n">
-        <v>4420</v>
+        <v>3773</v>
       </c>
       <c r="D4" t="n">
-        <v>10324</v>
+        <v>7286</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2568</v>
+        <v>2026</v>
       </c>
       <c r="C5" t="n">
-        <v>4349</v>
+        <v>3834</v>
       </c>
       <c r="D5" t="n">
-        <v>4262</v>
+        <v>3202</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1657</v>
+        <v>1384</v>
       </c>
       <c r="C6" t="n">
-        <v>3311</v>
+        <v>3730</v>
       </c>
       <c r="D6" t="n">
-        <v>1747</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>886</v>
+        <v>802</v>
       </c>
       <c r="C7" t="n">
-        <v>2045</v>
+        <v>2980</v>
       </c>
       <c r="D7" t="n">
-        <v>823</v>
+        <v>777</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>406</v>
+        <v>383</v>
       </c>
       <c r="C8" t="n">
-        <v>1130</v>
+        <v>1887</v>
       </c>
       <c r="D8" t="n">
-        <v>495</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C9" t="n">
-        <v>582</v>
+        <v>929</v>
       </c>
       <c r="D9" t="n">
         <v>335</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>301</v>
+        <v>395</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8627</v>
+        <v>8289</v>
       </c>
       <c r="C2" t="n">
-        <v>4539</v>
+        <v>7607</v>
       </c>
       <c r="D2" t="n">
-        <v>36426</v>
+        <v>18148</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6138</v>
+        <v>5575</v>
       </c>
       <c r="C3" t="n">
-        <v>6652</v>
+        <v>8928</v>
       </c>
       <c r="D3" t="n">
-        <v>22504</v>
+        <v>14976</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2372</v>
+        <v>1872</v>
       </c>
       <c r="C4" t="n">
-        <v>6678</v>
+        <v>5817</v>
       </c>
       <c r="D4" t="n">
-        <v>9743</v>
+        <v>7008</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1531</v>
+        <v>1278</v>
       </c>
       <c r="C5" t="n">
-        <v>3244</v>
+        <v>3655</v>
       </c>
       <c r="D5" t="n">
-        <v>2898</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>818</v>
+        <v>741</v>
       </c>
       <c r="C6" t="n">
-        <v>2004</v>
+        <v>2920</v>
       </c>
       <c r="D6" t="n">
-        <v>806</v>
+        <v>761</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>375</v>
+        <v>353</v>
       </c>
       <c r="C7" t="n">
-        <v>1107</v>
+        <v>1849</v>
       </c>
       <c r="D7" t="n">
-        <v>485</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C8" t="n">
-        <v>570</v>
+        <v>910</v>
       </c>
       <c r="D8" t="n">
         <v>328</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>294</v>
+        <v>387</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5328</v>
+        <v>5053</v>
       </c>
       <c r="C2" t="n">
-        <v>2088</v>
+        <v>4074</v>
       </c>
       <c r="D2" t="n">
-        <v>25172</v>
+        <v>12819</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6228</v>
+        <v>5806</v>
       </c>
       <c r="C3" t="n">
-        <v>5145</v>
+        <v>7535</v>
       </c>
       <c r="D3" t="n">
-        <v>23101</v>
+        <v>14544</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3325</v>
+        <v>2842</v>
       </c>
       <c r="C4" t="n">
-        <v>6719</v>
+        <v>7326</v>
       </c>
       <c r="D4" t="n">
-        <v>11593</v>
+        <v>8153</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1742</v>
+        <v>1430</v>
       </c>
       <c r="C5" t="n">
-        <v>4782</v>
+        <v>4667</v>
       </c>
       <c r="D5" t="n">
-        <v>3719</v>
+        <v>2893</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>991</v>
+        <v>885</v>
       </c>
       <c r="C6" t="n">
-        <v>2566</v>
+        <v>3358</v>
       </c>
       <c r="D6" t="n">
-        <v>1020</v>
+        <v>925</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="C7" t="n">
-        <v>1439</v>
+        <v>2287</v>
       </c>
       <c r="D7" t="n">
-        <v>530</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -2108,10 +2108,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C8" t="n">
-        <v>751</v>
+        <v>1208</v>
       </c>
       <c r="D8" t="n">
         <v>342</v>
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>342</v>
+        <v>444</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6693</v>
+        <v>5451</v>
       </c>
       <c r="C2" t="n">
-        <v>3748</v>
+        <v>6061</v>
       </c>
       <c r="D2" t="n">
-        <v>25357</v>
+        <v>14129</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4953</v>
+        <v>4647</v>
       </c>
       <c r="C3" t="n">
-        <v>3256</v>
+        <v>5199</v>
       </c>
       <c r="D3" t="n">
-        <v>21809</v>
+        <v>13294</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3928</v>
+        <v>3530</v>
       </c>
       <c r="C4" t="n">
-        <v>5793</v>
+        <v>7277</v>
       </c>
       <c r="D4" t="n">
-        <v>13229</v>
+        <v>9009</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2147</v>
+        <v>1800</v>
       </c>
       <c r="C5" t="n">
-        <v>5612</v>
+        <v>5846</v>
       </c>
       <c r="D5" t="n">
-        <v>4890</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1209</v>
+        <v>1036</v>
       </c>
       <c r="C6" t="n">
-        <v>3586</v>
+        <v>3960</v>
       </c>
       <c r="D6" t="n">
-        <v>1420</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>530</v>
+        <v>485</v>
       </c>
       <c r="C7" t="n">
-        <v>1949</v>
+        <v>2780</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C8" t="n">
-        <v>1041</v>
+        <v>1663</v>
       </c>
       <c r="D8" t="n">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>501</v>
+        <v>740</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>267</v>
+        <v>310</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>169</v>
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2537,7 +2537,7 @@
         <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3928</v>
+        <v>3192</v>
       </c>
       <c r="C2" t="n">
-        <v>1722</v>
+        <v>2807</v>
       </c>
       <c r="D2" t="n">
-        <v>17499</v>
+        <v>9755</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5193</v>
+        <v>4673</v>
       </c>
       <c r="C3" t="n">
-        <v>3321</v>
+        <v>5329</v>
       </c>
       <c r="D3" t="n">
-        <v>21682</v>
+        <v>13068</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4356</v>
+        <v>3917</v>
       </c>
       <c r="C4" t="n">
-        <v>5376</v>
+        <v>7126</v>
       </c>
       <c r="D4" t="n">
-        <v>14285</v>
+        <v>9578</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2221</v>
+        <v>1873</v>
       </c>
       <c r="C5" t="n">
-        <v>6430</v>
+        <v>6981</v>
       </c>
       <c r="D5" t="n">
-        <v>5341</v>
+        <v>3993</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>992</v>
+        <v>878</v>
       </c>
       <c r="C6" t="n">
-        <v>4342</v>
+        <v>4962</v>
       </c>
       <c r="D6" t="n">
-        <v>1392</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>2011</v>
+        <v>2988</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>817</v>
+        <v>1246</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>261</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
         <v>165</v>
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2834,7 +2834,7 @@
         <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4856</v>
+        <v>3463</v>
       </c>
       <c r="C2" t="n">
-        <v>1686</v>
+        <v>6891</v>
       </c>
       <c r="D2" t="n">
-        <v>15342</v>
+        <v>12387</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3974</v>
+        <v>3461</v>
       </c>
       <c r="C3" t="n">
-        <v>2296</v>
+        <v>3652</v>
       </c>
       <c r="D3" t="n">
-        <v>19656</v>
+        <v>11739</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4107</v>
+        <v>3695</v>
       </c>
       <c r="C4" t="n">
-        <v>4277</v>
+        <v>6166</v>
       </c>
       <c r="D4" t="n">
-        <v>15057</v>
+        <v>9856</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2748</v>
+        <v>2394</v>
       </c>
       <c r="C5" t="n">
-        <v>5872</v>
+        <v>6969</v>
       </c>
       <c r="D5" t="n">
-        <v>6552</v>
+        <v>4729</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1337</v>
+        <v>1155</v>
       </c>
       <c r="C6" t="n">
-        <v>5245</v>
+        <v>5836</v>
       </c>
       <c r="D6" t="n">
-        <v>1955</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="C7" t="n">
-        <v>3009</v>
+        <v>3857</v>
       </c>
       <c r="D7" t="n">
-        <v>693</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>1277</v>
+        <v>1918</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>453</v>
+        <v>625</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3145,7 +3145,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3383</v>
+        <v>2485</v>
       </c>
       <c r="C2" t="n">
-        <v>1430</v>
+        <v>3474</v>
       </c>
       <c r="D2" t="n">
-        <v>11970</v>
+        <v>9828</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3734</v>
+        <v>3031</v>
       </c>
       <c r="C3" t="n">
-        <v>1854</v>
+        <v>4534</v>
       </c>
       <c r="D3" t="n">
-        <v>18069</v>
+        <v>11178</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3708</v>
+        <v>3338</v>
       </c>
       <c r="C4" t="n">
-        <v>3474</v>
+        <v>5118</v>
       </c>
       <c r="D4" t="n">
-        <v>15361</v>
+        <v>9904</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3023</v>
+        <v>2626</v>
       </c>
       <c r="C5" t="n">
-        <v>5378</v>
+        <v>6791</v>
       </c>
       <c r="D5" t="n">
-        <v>7458</v>
+        <v>5266</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1602</v>
+        <v>1388</v>
       </c>
       <c r="C6" t="n">
-        <v>5663</v>
+        <v>6440</v>
       </c>
       <c r="D6" t="n">
-        <v>2367</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>355</v>
+        <v>322</v>
       </c>
       <c r="C7" t="n">
-        <v>3783</v>
+        <v>4624</v>
       </c>
       <c r="D7" t="n">
-        <v>788</v>
+        <v>728</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>1690</v>
+        <v>2433</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>549</v>
+        <v>747</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3442,7 +3442,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4621</v>
+        <v>4626</v>
       </c>
       <c r="C2" t="n">
-        <v>7357</v>
+        <v>13520</v>
       </c>
       <c r="D2" t="n">
-        <v>17440</v>
+        <v>13824</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3032</v>
+        <v>2382</v>
       </c>
       <c r="C3" t="n">
-        <v>1487</v>
+        <v>3672</v>
       </c>
       <c r="D3" t="n">
-        <v>16276</v>
+        <v>10379</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3230</v>
+        <v>2832</v>
       </c>
       <c r="C4" t="n">
-        <v>2686</v>
+        <v>4759</v>
       </c>
       <c r="D4" t="n">
-        <v>15136</v>
+        <v>9691</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3005</v>
+        <v>2616</v>
       </c>
       <c r="C5" t="n">
-        <v>4461</v>
+        <v>5959</v>
       </c>
       <c r="D5" t="n">
-        <v>8369</v>
+        <v>5773</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1944</v>
+        <v>1687</v>
       </c>
       <c r="C6" t="n">
-        <v>5498</v>
+        <v>6522</v>
       </c>
       <c r="D6" t="n">
-        <v>3020</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>672</v>
+        <v>592</v>
       </c>
       <c r="C7" t="n">
-        <v>4555</v>
+        <v>5316</v>
       </c>
       <c r="D7" t="n">
-        <v>981</v>
+        <v>866</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>2448</v>
+        <v>3250</v>
       </c>
       <c r="D8" t="n">
-        <v>470</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>945</v>
+        <v>1315</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>326</v>
+        <v>391</v>
       </c>
       <c r="D10" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3753,7 +3753,7 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6482</v>
+        <v>6266</v>
       </c>
       <c r="C2" t="n">
-        <v>3683</v>
+        <v>6088</v>
       </c>
       <c r="D2" t="n">
-        <v>9603</v>
+        <v>10379</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3275</v>
+        <v>3272</v>
       </c>
       <c r="C2" t="n">
-        <v>4119</v>
+        <v>7572</v>
       </c>
       <c r="D2" t="n">
-        <v>12836</v>
+        <v>10174</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4017</v>
+        <v>3366</v>
       </c>
       <c r="C3" t="n">
-        <v>3021</v>
+        <v>6346</v>
       </c>
       <c r="D3" t="n">
-        <v>17612</v>
+        <v>11499</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4426</v>
+        <v>3840</v>
       </c>
       <c r="C4" t="n">
-        <v>4077</v>
+        <v>6765</v>
       </c>
       <c r="D4" t="n">
-        <v>15586</v>
+        <v>9982</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1907</v>
+        <v>1655</v>
       </c>
       <c r="C5" t="n">
-        <v>7157</v>
+        <v>8996</v>
       </c>
       <c r="D5" t="n">
-        <v>7585</v>
+        <v>5341</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>620</v>
+        <v>547</v>
       </c>
       <c r="C6" t="n">
-        <v>5649</v>
+        <v>6551</v>
       </c>
       <c r="D6" t="n">
-        <v>2306</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C7" t="n">
-        <v>2399</v>
+        <v>3185</v>
       </c>
       <c r="D7" t="n">
-        <v>595</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>926</v>
+        <v>1288</v>
       </c>
       <c r="D8" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>319</v>
+        <v>383</v>
       </c>
       <c r="D9" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4361,7 +4361,7 @@
         <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6889</v>
+        <v>6896</v>
       </c>
       <c r="C2" t="n">
-        <v>3886</v>
+        <v>8370</v>
       </c>
       <c r="D2" t="n">
-        <v>19867</v>
+        <v>13254</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2753</v>
+        <v>2662</v>
       </c>
       <c r="C3" t="n">
-        <v>1856</v>
+        <v>3068</v>
       </c>
       <c r="D3" t="n">
-        <v>2252</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4557,7 +4557,7 @@
         <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5214</v>
+        <v>4499</v>
       </c>
       <c r="C2" t="n">
-        <v>4567</v>
+        <v>8758</v>
       </c>
       <c r="D2" t="n">
-        <v>24092</v>
+        <v>17966</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3960</v>
+        <v>3924</v>
       </c>
       <c r="C3" t="n">
-        <v>2622</v>
+        <v>5233</v>
       </c>
       <c r="D3" t="n">
-        <v>5045</v>
+        <v>4033</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1229</v>
+        <v>1190</v>
       </c>
       <c r="C4" t="n">
-        <v>1130</v>
+        <v>1841</v>
       </c>
       <c r="D4" t="n">
-        <v>1635</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
         <v>864</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5338</v>
+        <v>5243</v>
       </c>
       <c r="C2" t="n">
-        <v>4345</v>
+        <v>4798</v>
       </c>
       <c r="D2" t="n">
-        <v>18928</v>
+        <v>17860</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3764</v>
+        <v>3468</v>
       </c>
       <c r="C3" t="n">
-        <v>3187</v>
+        <v>6193</v>
       </c>
       <c r="D3" t="n">
-        <v>7729</v>
+        <v>5971</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2197</v>
+        <v>2175</v>
       </c>
       <c r="C4" t="n">
-        <v>1951</v>
+        <v>3723</v>
       </c>
       <c r="D4" t="n">
-        <v>2240</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="C5" t="n">
-        <v>711</v>
+        <v>1102</v>
       </c>
       <c r="D5" t="n">
-        <v>1220</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
         <v>910</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -5218,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
         <v>358</v>
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
         <v>372</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5280,7 +5280,7 @@
         <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6002</v>
+        <v>5297</v>
       </c>
       <c r="C2" t="n">
-        <v>5772</v>
+        <v>7128</v>
       </c>
       <c r="D2" t="n">
-        <v>30761</v>
+        <v>14864</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3706</v>
+        <v>3537</v>
       </c>
       <c r="C3" t="n">
-        <v>3296</v>
+        <v>4765</v>
       </c>
       <c r="D3" t="n">
-        <v>8887</v>
+        <v>7357</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2518</v>
+        <v>2407</v>
       </c>
       <c r="C4" t="n">
-        <v>2586</v>
+        <v>4973</v>
       </c>
       <c r="D4" t="n">
-        <v>3151</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1152</v>
+        <v>1112</v>
       </c>
       <c r="C5" t="n">
-        <v>1350</v>
+        <v>2427</v>
       </c>
       <c r="D5" t="n">
-        <v>1368</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C6" t="n">
-        <v>504</v>
+        <v>705</v>
       </c>
       <c r="D6" t="n">
         <v>951</v>
@@ -5515,7 +5515,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
         <v>484</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
         <v>378</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5591,7 +5591,7 @@
         <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8725</v>
+        <v>5791</v>
       </c>
       <c r="C2" t="n">
-        <v>8969</v>
+        <v>5445</v>
       </c>
       <c r="D2" t="n">
-        <v>29107</v>
+        <v>16915</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3523</v>
+        <v>3194</v>
       </c>
       <c r="C3" t="n">
-        <v>3754</v>
+        <v>4892</v>
       </c>
       <c r="D3" t="n">
-        <v>10899</v>
+        <v>7508</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1945</v>
+        <v>1833</v>
       </c>
       <c r="C4" t="n">
-        <v>2447</v>
+        <v>3942</v>
       </c>
       <c r="D4" t="n">
-        <v>3552</v>
+        <v>3033</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>957</v>
+        <v>925</v>
       </c>
       <c r="C5" t="n">
-        <v>1456</v>
+        <v>2760</v>
       </c>
       <c r="D5" t="n">
-        <v>1339</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="C6" t="n">
-        <v>632</v>
+        <v>1059</v>
       </c>
       <c r="D6" t="n">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>274</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
         <v>364</v>
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
         <v>270</v>
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7770</v>
+        <v>5691</v>
       </c>
       <c r="C2" t="n">
-        <v>6452</v>
+        <v>5522</v>
       </c>
       <c r="D2" t="n">
-        <v>30598</v>
+        <v>24154</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5149</v>
+        <v>3734</v>
       </c>
       <c r="C3" t="n">
-        <v>5889</v>
+        <v>4478</v>
       </c>
       <c r="D3" t="n">
-        <v>13284</v>
+        <v>8599</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2416</v>
+        <v>2207</v>
       </c>
       <c r="C4" t="n">
-        <v>3199</v>
+        <v>4443</v>
       </c>
       <c r="D4" t="n">
-        <v>4995</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1303</v>
+        <v>1223</v>
       </c>
       <c r="C5" t="n">
-        <v>2001</v>
+        <v>3406</v>
       </c>
       <c r="D5" t="n">
-        <v>1744</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>605</v>
+        <v>585</v>
       </c>
       <c r="C6" t="n">
-        <v>1106</v>
+        <v>2025</v>
       </c>
       <c r="D6" t="n">
-        <v>860</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="C7" t="n">
-        <v>480</v>
+        <v>745</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>250</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
         <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6199,7 +6199,7 @@
         <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6195</v>
+        <v>6099</v>
       </c>
       <c r="C2" t="n">
-        <v>6444</v>
+        <v>4122</v>
       </c>
       <c r="D2" t="n">
-        <v>37441</v>
+        <v>27316</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5301</v>
+        <v>3898</v>
       </c>
       <c r="C3" t="n">
-        <v>5358</v>
+        <v>4368</v>
       </c>
       <c r="D3" t="n">
-        <v>15097</v>
+        <v>10468</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3263</v>
+        <v>2536</v>
       </c>
       <c r="C4" t="n">
-        <v>4681</v>
+        <v>4327</v>
       </c>
       <c r="D4" t="n">
-        <v>6386</v>
+        <v>4634</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1626</v>
+        <v>1512</v>
       </c>
       <c r="C5" t="n">
-        <v>2626</v>
+        <v>3912</v>
       </c>
       <c r="D5" t="n">
-        <v>2315</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>873</v>
+        <v>817</v>
       </c>
       <c r="C6" t="n">
-        <v>1563</v>
+        <v>2743</v>
       </c>
       <c r="D6" t="n">
-        <v>1009</v>
+        <v>956</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="C7" t="n">
-        <v>817</v>
+        <v>1422</v>
       </c>
       <c r="D7" t="n">
-        <v>604</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>369</v>
+        <v>515</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -6479,7 +6479,7 @@
         <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="D9" t="n">
         <v>295</v>
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_95_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_95_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7751</v>
+        <v>4024</v>
       </c>
       <c r="C2" t="n">
-        <v>5261</v>
+        <v>8405</v>
       </c>
       <c r="D2" t="n">
-        <v>25511</v>
+        <v>22810</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4037</v>
+        <v>2865</v>
       </c>
       <c r="C3" t="n">
-        <v>3700</v>
+        <v>8572</v>
       </c>
       <c r="D3" t="n">
-        <v>12291</v>
+        <v>12145</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2737</v>
+        <v>2687</v>
       </c>
       <c r="C4" t="n">
-        <v>4258</v>
+        <v>6323</v>
       </c>
       <c r="D4" t="n">
-        <v>5557</v>
+        <v>5760</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1747</v>
+        <v>1777</v>
       </c>
       <c r="C5" t="n">
-        <v>4004</v>
+        <v>4519</v>
       </c>
       <c r="D5" t="n">
-        <v>2335</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1038</v>
+        <v>923</v>
       </c>
       <c r="C6" t="n">
-        <v>3296</v>
+        <v>3118</v>
       </c>
       <c r="D6" t="n">
-        <v>1114</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>507</v>
+        <v>419</v>
       </c>
       <c r="C7" t="n">
-        <v>2068</v>
+        <v>1823</v>
       </c>
       <c r="D7" t="n">
-        <v>649</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="C8" t="n">
-        <v>936</v>
+        <v>817</v>
       </c>
       <c r="D8" t="n">
         <v>434</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>369</v>
+        <v>339</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -948,7 +948,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>77</v>
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7313</v>
+        <v>5642</v>
       </c>
       <c r="C2" t="n">
-        <v>11250</v>
+        <v>8755</v>
       </c>
       <c r="D2" t="n">
-        <v>25028</v>
+        <v>21774</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4599</v>
+        <v>2767</v>
       </c>
       <c r="C3" t="n">
-        <v>3886</v>
+        <v>7461</v>
       </c>
       <c r="D3" t="n">
-        <v>13262</v>
+        <v>12779</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2820</v>
+        <v>2375</v>
       </c>
       <c r="C4" t="n">
-        <v>3896</v>
+        <v>7292</v>
       </c>
       <c r="D4" t="n">
-        <v>6433</v>
+        <v>6571</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1924</v>
+        <v>1940</v>
       </c>
       <c r="C5" t="n">
-        <v>4001</v>
+        <v>5230</v>
       </c>
       <c r="D5" t="n">
-        <v>2789</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1240</v>
+        <v>1169</v>
       </c>
       <c r="C6" t="n">
-        <v>3589</v>
+        <v>3732</v>
       </c>
       <c r="D6" t="n">
-        <v>1275</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>659</v>
+        <v>567</v>
       </c>
       <c r="C7" t="n">
-        <v>2600</v>
+        <v>2388</v>
       </c>
       <c r="D7" t="n">
-        <v>715</v>
+        <v>696</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>285</v>
+        <v>235</v>
       </c>
       <c r="C8" t="n">
-        <v>1434</v>
+        <v>1260</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>604</v>
+        <v>536</v>
       </c>
       <c r="D9" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9106</v>
+        <v>6826</v>
       </c>
       <c r="C2" t="n">
-        <v>11321</v>
+        <v>10137</v>
       </c>
       <c r="D2" t="n">
-        <v>22019</v>
+        <v>20057</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4671</v>
+        <v>3176</v>
       </c>
       <c r="C3" t="n">
-        <v>6244</v>
+        <v>7089</v>
       </c>
       <c r="D3" t="n">
-        <v>13898</v>
+        <v>13092</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3041</v>
+        <v>2170</v>
       </c>
       <c r="C4" t="n">
-        <v>3773</v>
+        <v>7144</v>
       </c>
       <c r="D4" t="n">
-        <v>7286</v>
+        <v>7324</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2026</v>
+        <v>1895</v>
       </c>
       <c r="C5" t="n">
-        <v>3834</v>
+        <v>6012</v>
       </c>
       <c r="D5" t="n">
-        <v>3202</v>
+        <v>3191</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1384</v>
+        <v>1347</v>
       </c>
       <c r="C6" t="n">
-        <v>3730</v>
+        <v>4280</v>
       </c>
       <c r="D6" t="n">
-        <v>1476</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>802</v>
+        <v>723</v>
       </c>
       <c r="C7" t="n">
-        <v>2980</v>
+        <v>2916</v>
       </c>
       <c r="D7" t="n">
-        <v>777</v>
+        <v>752</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>383</v>
+        <v>325</v>
       </c>
       <c r="C8" t="n">
-        <v>1887</v>
+        <v>1712</v>
       </c>
       <c r="D8" t="n">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="C9" t="n">
-        <v>929</v>
+        <v>807</v>
       </c>
       <c r="D9" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>395</v>
+        <v>363</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
         <v>127</v>
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8289</v>
+        <v>6145</v>
       </c>
       <c r="C2" t="n">
-        <v>7607</v>
+        <v>6893</v>
       </c>
       <c r="D2" t="n">
-        <v>18148</v>
+        <v>16548</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5575</v>
+        <v>3878</v>
       </c>
       <c r="C3" t="n">
-        <v>8928</v>
+        <v>10902</v>
       </c>
       <c r="D3" t="n">
-        <v>14976</v>
+        <v>14245</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1872</v>
+        <v>1750</v>
       </c>
       <c r="C4" t="n">
-        <v>5817</v>
+        <v>9749</v>
       </c>
       <c r="D4" t="n">
-        <v>7008</v>
+        <v>7057</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1278</v>
+        <v>1244</v>
       </c>
       <c r="C5" t="n">
-        <v>3655</v>
+        <v>4194</v>
       </c>
       <c r="D5" t="n">
-        <v>2337</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>741</v>
+        <v>668</v>
       </c>
       <c r="C6" t="n">
-        <v>2920</v>
+        <v>2857</v>
       </c>
       <c r="D6" t="n">
-        <v>761</v>
+        <v>736</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>353</v>
+        <v>300</v>
       </c>
       <c r="C7" t="n">
-        <v>1849</v>
+        <v>1677</v>
       </c>
       <c r="D7" t="n">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>910</v>
+        <v>790</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>387</v>
+        <v>355</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
         <v>124</v>
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5053</v>
+        <v>3756</v>
       </c>
       <c r="C2" t="n">
-        <v>4074</v>
+        <v>3323</v>
       </c>
       <c r="D2" t="n">
-        <v>12819</v>
+        <v>12325</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5806</v>
+        <v>4163</v>
       </c>
       <c r="C3" t="n">
-        <v>7535</v>
+        <v>8205</v>
       </c>
       <c r="D3" t="n">
-        <v>14544</v>
+        <v>13737</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2842</v>
+        <v>2274</v>
       </c>
       <c r="C4" t="n">
-        <v>7326</v>
+        <v>10462</v>
       </c>
       <c r="D4" t="n">
-        <v>8153</v>
+        <v>8082</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1430</v>
+        <v>1361</v>
       </c>
       <c r="C5" t="n">
-        <v>4667</v>
+        <v>6560</v>
       </c>
       <c r="D5" t="n">
-        <v>2893</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>885</v>
+        <v>808</v>
       </c>
       <c r="C6" t="n">
-        <v>3358</v>
+        <v>3505</v>
       </c>
       <c r="D6" t="n">
-        <v>925</v>
+        <v>893</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333</v>
+        <v>282</v>
       </c>
       <c r="C7" t="n">
-        <v>2287</v>
+        <v>2148</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>1208</v>
+        <v>1046</v>
       </c>
       <c r="D8" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5451</v>
+        <v>3344</v>
       </c>
       <c r="C2" t="n">
-        <v>6061</v>
+        <v>4345</v>
       </c>
       <c r="D2" t="n">
-        <v>14129</v>
+        <v>16483</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4647</v>
+        <v>3349</v>
       </c>
       <c r="C3" t="n">
-        <v>5199</v>
+        <v>5163</v>
       </c>
       <c r="D3" t="n">
-        <v>13294</v>
+        <v>12720</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3530</v>
+        <v>2671</v>
       </c>
       <c r="C4" t="n">
-        <v>7277</v>
+        <v>9218</v>
       </c>
       <c r="D4" t="n">
-        <v>9009</v>
+        <v>8759</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1800</v>
+        <v>1560</v>
       </c>
       <c r="C5" t="n">
-        <v>5846</v>
+        <v>8259</v>
       </c>
       <c r="D5" t="n">
-        <v>3663</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1036</v>
+        <v>952</v>
       </c>
       <c r="C6" t="n">
-        <v>3960</v>
+        <v>4883</v>
       </c>
       <c r="D6" t="n">
-        <v>1214</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>485</v>
+        <v>431</v>
       </c>
       <c r="C7" t="n">
-        <v>2780</v>
+        <v>2732</v>
       </c>
       <c r="D7" t="n">
-        <v>573</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="C8" t="n">
-        <v>1663</v>
+        <v>1509</v>
       </c>
       <c r="D8" t="n">
-        <v>366</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>740</v>
+        <v>660</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="D10" t="n">
         <v>216</v>
@@ -2467,7 +2467,7 @@
         <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
         <v>64</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3192</v>
+        <v>1993</v>
       </c>
       <c r="C2" t="n">
-        <v>2807</v>
+        <v>2074</v>
       </c>
       <c r="D2" t="n">
-        <v>9755</v>
+        <v>11490</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4673</v>
+        <v>3229</v>
       </c>
       <c r="C3" t="n">
-        <v>5329</v>
+        <v>4731</v>
       </c>
       <c r="D3" t="n">
-        <v>13068</v>
+        <v>12826</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3917</v>
+        <v>2963</v>
       </c>
       <c r="C4" t="n">
-        <v>7126</v>
+        <v>8587</v>
       </c>
       <c r="D4" t="n">
-        <v>9578</v>
+        <v>9289</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1873</v>
+        <v>1645</v>
       </c>
       <c r="C5" t="n">
-        <v>6981</v>
+        <v>9639</v>
       </c>
       <c r="D5" t="n">
-        <v>3993</v>
+        <v>3718</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>878</v>
+        <v>785</v>
       </c>
       <c r="C6" t="n">
-        <v>4962</v>
+        <v>5878</v>
       </c>
       <c r="D6" t="n">
-        <v>1193</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="C7" t="n">
-        <v>2988</v>
+        <v>2840</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1246</v>
+        <v>1105</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -2747,7 +2747,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
         <v>289</v>
@@ -2764,7 +2764,7 @@
         <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3463</v>
+        <v>3465</v>
       </c>
       <c r="C2" t="n">
-        <v>6891</v>
+        <v>8023</v>
       </c>
       <c r="D2" t="n">
-        <v>12387</v>
+        <v>14092</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3461</v>
+        <v>2331</v>
       </c>
       <c r="C3" t="n">
-        <v>3652</v>
+        <v>3100</v>
       </c>
       <c r="D3" t="n">
-        <v>11739</v>
+        <v>11782</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3695</v>
+        <v>2688</v>
       </c>
       <c r="C4" t="n">
-        <v>6166</v>
+        <v>6639</v>
       </c>
       <c r="D4" t="n">
-        <v>9856</v>
+        <v>9673</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2394</v>
+        <v>1942</v>
       </c>
       <c r="C5" t="n">
-        <v>6969</v>
+        <v>9056</v>
       </c>
       <c r="D5" t="n">
-        <v>4729</v>
+        <v>4407</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1155</v>
+        <v>1015</v>
       </c>
       <c r="C6" t="n">
-        <v>5836</v>
+        <v>7470</v>
       </c>
       <c r="D6" t="n">
-        <v>1592</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>342</v>
+        <v>291</v>
       </c>
       <c r="C7" t="n">
-        <v>3857</v>
+        <v>4115</v>
       </c>
       <c r="D7" t="n">
-        <v>653</v>
+        <v>642</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>1918</v>
+        <v>1755</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>625</v>
+        <v>557</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2485</v>
+        <v>2241</v>
       </c>
       <c r="C2" t="n">
-        <v>3474</v>
+        <v>4528</v>
       </c>
       <c r="D2" t="n">
-        <v>9828</v>
+        <v>10559</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3031</v>
+        <v>2360</v>
       </c>
       <c r="C3" t="n">
-        <v>4534</v>
+        <v>4614</v>
       </c>
       <c r="D3" t="n">
-        <v>11178</v>
+        <v>11418</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3338</v>
+        <v>2359</v>
       </c>
       <c r="C4" t="n">
-        <v>5118</v>
+        <v>5201</v>
       </c>
       <c r="D4" t="n">
-        <v>9904</v>
+        <v>9755</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2626</v>
+        <v>2087</v>
       </c>
       <c r="C5" t="n">
-        <v>6791</v>
+        <v>8333</v>
       </c>
       <c r="D5" t="n">
-        <v>5266</v>
+        <v>4964</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1388</v>
+        <v>1192</v>
       </c>
       <c r="C6" t="n">
-        <v>6440</v>
+        <v>8272</v>
       </c>
       <c r="D6" t="n">
-        <v>1875</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>322</v>
+        <v>263</v>
       </c>
       <c r="C7" t="n">
-        <v>4624</v>
+        <v>5217</v>
       </c>
       <c r="D7" t="n">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>2433</v>
+        <v>2306</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>747</v>
+        <v>651</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
+        <v>133</v>
+      </c>
+      <c r="D11" t="n">
         <v>137</v>
-      </c>
-      <c r="D11" t="n">
-        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4626</v>
+        <v>3148</v>
       </c>
       <c r="C2" t="n">
-        <v>13520</v>
+        <v>9457</v>
       </c>
       <c r="D2" t="n">
-        <v>13824</v>
+        <v>12644</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2382</v>
+        <v>1950</v>
       </c>
       <c r="C3" t="n">
-        <v>3672</v>
+        <v>4110</v>
       </c>
       <c r="D3" t="n">
-        <v>10379</v>
+        <v>10584</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2832</v>
+        <v>2070</v>
       </c>
       <c r="C4" t="n">
-        <v>4759</v>
+        <v>4844</v>
       </c>
       <c r="D4" t="n">
-        <v>9691</v>
+        <v>9697</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2616</v>
+        <v>1993</v>
       </c>
       <c r="C5" t="n">
-        <v>5959</v>
+        <v>6896</v>
       </c>
       <c r="D5" t="n">
-        <v>5773</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1687</v>
+        <v>1390</v>
       </c>
       <c r="C6" t="n">
-        <v>6522</v>
+        <v>8225</v>
       </c>
       <c r="D6" t="n">
-        <v>2306</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>592</v>
+        <v>490</v>
       </c>
       <c r="C7" t="n">
-        <v>5316</v>
+        <v>6352</v>
       </c>
       <c r="D7" t="n">
-        <v>866</v>
+        <v>829</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>3250</v>
+        <v>3354</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1315</v>
+        <v>1192</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>391</v>
+        <v>351</v>
       </c>
       <c r="D10" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6266</v>
+        <v>4039</v>
       </c>
       <c r="C2" t="n">
-        <v>6088</v>
+        <v>4445</v>
       </c>
       <c r="D2" t="n">
-        <v>10379</v>
+        <v>5566</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3272</v>
+        <v>2250</v>
       </c>
       <c r="C2" t="n">
-        <v>7572</v>
+        <v>5447</v>
       </c>
       <c r="D2" t="n">
-        <v>10174</v>
+        <v>9305</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3366</v>
+        <v>2608</v>
       </c>
       <c r="C3" t="n">
-        <v>6346</v>
+        <v>5669</v>
       </c>
       <c r="D3" t="n">
-        <v>11499</v>
+        <v>11621</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3840</v>
+        <v>2879</v>
       </c>
       <c r="C4" t="n">
-        <v>6765</v>
+        <v>7229</v>
       </c>
       <c r="D4" t="n">
-        <v>9982</v>
+        <v>9967</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1655</v>
+        <v>1339</v>
       </c>
       <c r="C5" t="n">
-        <v>8996</v>
+        <v>10883</v>
       </c>
       <c r="D5" t="n">
-        <v>5341</v>
+        <v>4975</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>547</v>
+        <v>452</v>
       </c>
       <c r="C6" t="n">
-        <v>6551</v>
+        <v>7837</v>
       </c>
       <c r="D6" t="n">
-        <v>1868</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>3185</v>
+        <v>3286</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1288</v>
+        <v>1168</v>
       </c>
       <c r="D8" t="n">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>383</v>
+        <v>343</v>
       </c>
       <c r="D9" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6896</v>
+        <v>6068</v>
       </c>
       <c r="C2" t="n">
-        <v>8370</v>
+        <v>7307</v>
       </c>
       <c r="D2" t="n">
-        <v>13254</v>
+        <v>11302</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2662</v>
+        <v>1718</v>
       </c>
       <c r="C3" t="n">
-        <v>3068</v>
+        <v>2275</v>
       </c>
       <c r="D3" t="n">
-        <v>2383</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4557,7 +4557,7 @@
         <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4499</v>
+        <v>3673</v>
       </c>
       <c r="C2" t="n">
-        <v>8758</v>
+        <v>6917</v>
       </c>
       <c r="D2" t="n">
-        <v>17966</v>
+        <v>13714</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3924</v>
+        <v>3241</v>
       </c>
       <c r="C3" t="n">
-        <v>5233</v>
+        <v>4454</v>
       </c>
       <c r="D3" t="n">
-        <v>4033</v>
+        <v>3125</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1190</v>
+        <v>780</v>
       </c>
       <c r="C4" t="n">
-        <v>1841</v>
+        <v>1397</v>
       </c>
       <c r="D4" t="n">
-        <v>1661</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4879,10 +4879,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
         <v>864</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4910,7 +4910,7 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
         <v>441</v>
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5008,7 +5008,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5243</v>
+        <v>5120</v>
       </c>
       <c r="C2" t="n">
-        <v>4798</v>
+        <v>7605</v>
       </c>
       <c r="D2" t="n">
-        <v>17860</v>
+        <v>22803</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3468</v>
+        <v>2849</v>
       </c>
       <c r="C3" t="n">
-        <v>6193</v>
+        <v>5073</v>
       </c>
       <c r="D3" t="n">
-        <v>5971</v>
+        <v>4594</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2175</v>
+        <v>1726</v>
       </c>
       <c r="C4" t="n">
-        <v>3723</v>
+        <v>3086</v>
       </c>
       <c r="D4" t="n">
-        <v>2065</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>538</v>
+        <v>381</v>
       </c>
       <c r="C5" t="n">
-        <v>1102</v>
+        <v>870</v>
       </c>
       <c r="D5" t="n">
-        <v>1225</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
         <v>910</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -5221,7 +5221,7 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
         <v>462</v>
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>116</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5297</v>
+        <v>5765</v>
       </c>
       <c r="C2" t="n">
-        <v>7128</v>
+        <v>5890</v>
       </c>
       <c r="D2" t="n">
-        <v>14864</v>
+        <v>21279</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3537</v>
+        <v>3211</v>
       </c>
       <c r="C3" t="n">
-        <v>4765</v>
+        <v>5562</v>
       </c>
       <c r="D3" t="n">
-        <v>7357</v>
+        <v>7038</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2407</v>
+        <v>1934</v>
       </c>
       <c r="C4" t="n">
-        <v>4973</v>
+        <v>4109</v>
       </c>
       <c r="D4" t="n">
-        <v>2714</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1112</v>
+        <v>873</v>
       </c>
       <c r="C5" t="n">
-        <v>2427</v>
+        <v>2021</v>
       </c>
       <c r="D5" t="n">
-        <v>1321</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="C6" t="n">
-        <v>705</v>
+        <v>585</v>
       </c>
       <c r="D6" t="n">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -5515,7 +5515,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
         <v>484</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
         <v>378</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5599,7 +5599,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
         <v>128</v>
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5791</v>
+        <v>6654</v>
       </c>
       <c r="C2" t="n">
-        <v>5445</v>
+        <v>8992</v>
       </c>
       <c r="D2" t="n">
-        <v>16915</v>
+        <v>22757</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3194</v>
+        <v>3252</v>
       </c>
       <c r="C3" t="n">
-        <v>4892</v>
+        <v>4692</v>
       </c>
       <c r="D3" t="n">
-        <v>7508</v>
+        <v>8191</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1833</v>
+        <v>1607</v>
       </c>
       <c r="C4" t="n">
-        <v>3942</v>
+        <v>4038</v>
       </c>
       <c r="D4" t="n">
-        <v>3033</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>925</v>
+        <v>732</v>
       </c>
       <c r="C5" t="n">
-        <v>2760</v>
+        <v>2272</v>
       </c>
       <c r="D5" t="n">
-        <v>1222</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>330</v>
+        <v>262</v>
       </c>
       <c r="C6" t="n">
-        <v>1059</v>
+        <v>891</v>
       </c>
       <c r="D6" t="n">
-        <v>771</v>
+        <v>757</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>334</v>
+        <v>300</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
         <v>364</v>
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
         <v>270</v>
@@ -5871,7 +5871,7 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5691</v>
+        <v>4592</v>
       </c>
       <c r="C2" t="n">
-        <v>5522</v>
+        <v>10664</v>
       </c>
       <c r="D2" t="n">
-        <v>24154</v>
+        <v>19320</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3734</v>
+        <v>4149</v>
       </c>
       <c r="C3" t="n">
-        <v>4478</v>
+        <v>6225</v>
       </c>
       <c r="D3" t="n">
-        <v>8599</v>
+        <v>10138</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2207</v>
+        <v>2153</v>
       </c>
       <c r="C4" t="n">
-        <v>4443</v>
+        <v>4355</v>
       </c>
       <c r="D4" t="n">
-        <v>3885</v>
+        <v>3713</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1223</v>
+        <v>1050</v>
       </c>
       <c r="C5" t="n">
-        <v>3406</v>
+        <v>3254</v>
       </c>
       <c r="D5" t="n">
-        <v>1549</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>585</v>
+        <v>461</v>
       </c>
       <c r="C6" t="n">
-        <v>2025</v>
+        <v>1688</v>
       </c>
       <c r="D6" t="n">
-        <v>839</v>
+        <v>811</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>745</v>
+        <v>641</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -6182,7 +6182,7 @@
         <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6199,7 +6199,7 @@
         <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
         <v>81</v>
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6099</v>
+        <v>3280</v>
       </c>
       <c r="C2" t="n">
-        <v>4122</v>
+        <v>12110</v>
       </c>
       <c r="D2" t="n">
-        <v>27316</v>
+        <v>24260</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3898</v>
+        <v>3604</v>
       </c>
       <c r="C3" t="n">
-        <v>4368</v>
+        <v>7509</v>
       </c>
       <c r="D3" t="n">
-        <v>10468</v>
+        <v>10877</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2536</v>
+        <v>2721</v>
       </c>
       <c r="C4" t="n">
-        <v>4327</v>
+        <v>5341</v>
       </c>
       <c r="D4" t="n">
-        <v>4634</v>
+        <v>4798</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1512</v>
+        <v>1394</v>
       </c>
       <c r="C5" t="n">
-        <v>3912</v>
+        <v>3799</v>
       </c>
       <c r="D5" t="n">
-        <v>1950</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>817</v>
+        <v>690</v>
       </c>
       <c r="C6" t="n">
-        <v>2743</v>
+        <v>2493</v>
       </c>
       <c r="D6" t="n">
-        <v>956</v>
+        <v>907</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>344</v>
+        <v>273</v>
       </c>
       <c r="C7" t="n">
-        <v>1422</v>
+        <v>1205</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>515</v>
+        <v>460</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_95_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_95_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4024</v>
+        <v>611</v>
       </c>
       <c r="C2" t="n">
-        <v>8405</v>
+        <v>2828</v>
       </c>
       <c r="D2" t="n">
-        <v>22810</v>
+        <v>17014</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2865</v>
+        <v>1291</v>
       </c>
       <c r="C3" t="n">
-        <v>8572</v>
+        <v>6607</v>
       </c>
       <c r="D3" t="n">
-        <v>12145</v>
+        <v>14030</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2687</v>
+        <v>995</v>
       </c>
       <c r="C4" t="n">
-        <v>6323</v>
+        <v>7446</v>
       </c>
       <c r="D4" t="n">
-        <v>5760</v>
+        <v>5888</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1777</v>
+        <v>431</v>
       </c>
       <c r="C5" t="n">
-        <v>4519</v>
+        <v>5732</v>
       </c>
       <c r="D5" t="n">
-        <v>2247</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>923</v>
+        <v>174</v>
       </c>
       <c r="C6" t="n">
-        <v>3118</v>
+        <v>2864</v>
       </c>
       <c r="D6" t="n">
-        <v>1049</v>
+        <v>743</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>419</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>1823</v>
+        <v>1036</v>
       </c>
       <c r="D7" t="n">
-        <v>639</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>156</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>817</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>339</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5642</v>
+        <v>680</v>
       </c>
       <c r="C2" t="n">
-        <v>8755</v>
+        <v>6483</v>
       </c>
       <c r="D2" t="n">
-        <v>21774</v>
+        <v>22423</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2767</v>
+        <v>834</v>
       </c>
       <c r="C3" t="n">
-        <v>7461</v>
+        <v>4080</v>
       </c>
       <c r="D3" t="n">
-        <v>12779</v>
+        <v>13495</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2375</v>
+        <v>978</v>
       </c>
       <c r="C4" t="n">
-        <v>7292</v>
+        <v>6911</v>
       </c>
       <c r="D4" t="n">
-        <v>6571</v>
+        <v>7194</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1940</v>
+        <v>607</v>
       </c>
       <c r="C5" t="n">
-        <v>5230</v>
+        <v>6484</v>
       </c>
       <c r="D5" t="n">
-        <v>2752</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1169</v>
+        <v>258</v>
       </c>
       <c r="C6" t="n">
-        <v>3732</v>
+        <v>4265</v>
       </c>
       <c r="D6" t="n">
-        <v>1208</v>
+        <v>922</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>567</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>2388</v>
+        <v>1905</v>
       </c>
       <c r="D7" t="n">
-        <v>696</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>235</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>1260</v>
+        <v>672</v>
       </c>
       <c r="D8" t="n">
-        <v>455</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>536</v>
+        <v>325</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6826</v>
+        <v>364</v>
       </c>
       <c r="C2" t="n">
-        <v>10137</v>
+        <v>2760</v>
       </c>
       <c r="D2" t="n">
-        <v>20057</v>
+        <v>15280</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3176</v>
+        <v>762</v>
       </c>
       <c r="C3" t="n">
-        <v>7089</v>
+        <v>4787</v>
       </c>
       <c r="D3" t="n">
-        <v>13092</v>
+        <v>14220</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2170</v>
+        <v>1050</v>
       </c>
       <c r="C4" t="n">
-        <v>7144</v>
+        <v>6409</v>
       </c>
       <c r="D4" t="n">
-        <v>7324</v>
+        <v>7986</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1895</v>
+        <v>595</v>
       </c>
       <c r="C5" t="n">
-        <v>6012</v>
+        <v>7435</v>
       </c>
       <c r="D5" t="n">
-        <v>3191</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1347</v>
+        <v>220</v>
       </c>
       <c r="C6" t="n">
-        <v>4280</v>
+        <v>5283</v>
       </c>
       <c r="D6" t="n">
-        <v>1414</v>
+        <v>940</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>723</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>2916</v>
+        <v>1772</v>
       </c>
       <c r="D7" t="n">
-        <v>752</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>325</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1712</v>
+        <v>548</v>
       </c>
       <c r="D8" t="n">
-        <v>483</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>126</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>807</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>363</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>209</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6145</v>
+        <v>701</v>
       </c>
       <c r="C2" t="n">
-        <v>6893</v>
+        <v>4020</v>
       </c>
       <c r="D2" t="n">
-        <v>16548</v>
+        <v>16685</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3878</v>
+        <v>501</v>
       </c>
       <c r="C3" t="n">
-        <v>10902</v>
+        <v>3328</v>
       </c>
       <c r="D3" t="n">
-        <v>14245</v>
+        <v>13394</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1750</v>
+        <v>824</v>
       </c>
       <c r="C4" t="n">
-        <v>9749</v>
+        <v>5496</v>
       </c>
       <c r="D4" t="n">
-        <v>7057</v>
+        <v>8820</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1244</v>
+        <v>706</v>
       </c>
       <c r="C5" t="n">
-        <v>4194</v>
+        <v>6849</v>
       </c>
       <c r="D5" t="n">
-        <v>2243</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>668</v>
+        <v>334</v>
       </c>
       <c r="C6" t="n">
-        <v>2857</v>
+        <v>6325</v>
       </c>
       <c r="D6" t="n">
-        <v>736</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>300</v>
+        <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>1677</v>
+        <v>3319</v>
       </c>
       <c r="D7" t="n">
-        <v>473</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>790</v>
+        <v>1038</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
+        <v>70</v>
+      </c>
+      <c r="D14" t="n">
         <v>67</v>
-      </c>
-      <c r="D14" t="n">
-        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3756</v>
+        <v>471</v>
       </c>
       <c r="C2" t="n">
-        <v>3323</v>
+        <v>3586</v>
       </c>
       <c r="D2" t="n">
-        <v>12325</v>
+        <v>11644</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4163</v>
+        <v>500</v>
       </c>
       <c r="C3" t="n">
-        <v>8205</v>
+        <v>3301</v>
       </c>
       <c r="D3" t="n">
-        <v>13737</v>
+        <v>13198</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2274</v>
+        <v>664</v>
       </c>
       <c r="C4" t="n">
-        <v>10462</v>
+        <v>4561</v>
       </c>
       <c r="D4" t="n">
-        <v>8082</v>
+        <v>9295</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1361</v>
+        <v>730</v>
       </c>
       <c r="C5" t="n">
-        <v>6560</v>
+        <v>6424</v>
       </c>
       <c r="D5" t="n">
-        <v>2818</v>
+        <v>4219</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>808</v>
+        <v>405</v>
       </c>
       <c r="C6" t="n">
-        <v>3505</v>
+        <v>6767</v>
       </c>
       <c r="D6" t="n">
-        <v>893</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>282</v>
+        <v>120</v>
       </c>
       <c r="C7" t="n">
-        <v>2148</v>
+        <v>4399</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1046</v>
+        <v>1589</v>
       </c>
       <c r="D8" t="n">
-        <v>341</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>410</v>
+        <v>460</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3344</v>
+        <v>717</v>
       </c>
       <c r="C2" t="n">
-        <v>4345</v>
+        <v>5029</v>
       </c>
       <c r="D2" t="n">
-        <v>16483</v>
+        <v>16590</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3349</v>
+        <v>410</v>
       </c>
       <c r="C3" t="n">
-        <v>5163</v>
+        <v>3050</v>
       </c>
       <c r="D3" t="n">
-        <v>12720</v>
+        <v>12099</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2671</v>
+        <v>526</v>
       </c>
       <c r="C4" t="n">
-        <v>9218</v>
+        <v>3873</v>
       </c>
       <c r="D4" t="n">
-        <v>8759</v>
+        <v>9649</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1560</v>
+        <v>647</v>
       </c>
       <c r="C5" t="n">
-        <v>8259</v>
+        <v>5449</v>
       </c>
       <c r="D5" t="n">
-        <v>3513</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>952</v>
+        <v>490</v>
       </c>
       <c r="C6" t="n">
-        <v>4883</v>
+        <v>6621</v>
       </c>
       <c r="D6" t="n">
-        <v>1185</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>431</v>
+        <v>199</v>
       </c>
       <c r="C7" t="n">
-        <v>2732</v>
+        <v>5371</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>767</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>144</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>1509</v>
+        <v>2705</v>
       </c>
       <c r="D8" t="n">
-        <v>359</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>660</v>
+        <v>873</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1993</v>
+        <v>487</v>
       </c>
       <c r="C2" t="n">
-        <v>2074</v>
+        <v>2656</v>
       </c>
       <c r="D2" t="n">
-        <v>11490</v>
+        <v>12077</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3229</v>
+        <v>587</v>
       </c>
       <c r="C3" t="n">
-        <v>4731</v>
+        <v>3827</v>
       </c>
       <c r="D3" t="n">
-        <v>12826</v>
+        <v>13272</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2963</v>
+        <v>857</v>
       </c>
       <c r="C4" t="n">
-        <v>8587</v>
+        <v>5651</v>
       </c>
       <c r="D4" t="n">
-        <v>9289</v>
+        <v>9875</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1645</v>
+        <v>488</v>
       </c>
       <c r="C5" t="n">
-        <v>9639</v>
+        <v>8697</v>
       </c>
       <c r="D5" t="n">
-        <v>3718</v>
+        <v>4485</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>785</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>5878</v>
+        <v>6820</v>
       </c>
       <c r="D6" t="n">
-        <v>1170</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="C7" t="n">
-        <v>2840</v>
+        <v>2650</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>1105</v>
+        <v>855</v>
       </c>
       <c r="D8" t="n">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3465</v>
+        <v>251</v>
       </c>
       <c r="C2" t="n">
-        <v>8023</v>
+        <v>2719</v>
       </c>
       <c r="D2" t="n">
-        <v>14092</v>
+        <v>9580</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2331</v>
+        <v>463</v>
       </c>
       <c r="C3" t="n">
-        <v>3100</v>
+        <v>2879</v>
       </c>
       <c r="D3" t="n">
-        <v>11782</v>
+        <v>12148</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2688</v>
+        <v>607</v>
       </c>
       <c r="C4" t="n">
-        <v>6639</v>
+        <v>4489</v>
       </c>
       <c r="D4" t="n">
-        <v>9673</v>
+        <v>9737</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1942</v>
+        <v>456</v>
       </c>
       <c r="C5" t="n">
-        <v>9056</v>
+        <v>6403</v>
       </c>
       <c r="D5" t="n">
-        <v>4407</v>
+        <v>4741</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1015</v>
+        <v>176</v>
       </c>
       <c r="C6" t="n">
-        <v>7470</v>
+        <v>6329</v>
       </c>
       <c r="D6" t="n">
-        <v>1497</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>4115</v>
+        <v>3195</v>
       </c>
       <c r="D7" t="n">
-        <v>642</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1755</v>
+        <v>989</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>557</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>124</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2241</v>
+        <v>360</v>
       </c>
       <c r="C2" t="n">
-        <v>4528</v>
+        <v>3561</v>
       </c>
       <c r="D2" t="n">
-        <v>10559</v>
+        <v>9970</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2360</v>
+        <v>305</v>
       </c>
       <c r="C3" t="n">
-        <v>4614</v>
+        <v>2422</v>
       </c>
       <c r="D3" t="n">
-        <v>11418</v>
+        <v>10979</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2359</v>
+        <v>469</v>
       </c>
       <c r="C4" t="n">
-        <v>5201</v>
+        <v>3542</v>
       </c>
       <c r="D4" t="n">
-        <v>9755</v>
+        <v>9787</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2087</v>
+        <v>477</v>
       </c>
       <c r="C5" t="n">
-        <v>8333</v>
+        <v>5259</v>
       </c>
       <c r="D5" t="n">
-        <v>4964</v>
+        <v>5508</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1192</v>
+        <v>276</v>
       </c>
       <c r="C6" t="n">
-        <v>8272</v>
+        <v>6359</v>
       </c>
       <c r="D6" t="n">
-        <v>1759</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>263</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>5217</v>
+        <v>4729</v>
       </c>
       <c r="D7" t="n">
-        <v>722</v>
+        <v>748</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>2306</v>
+        <v>2035</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>651</v>
+        <v>602</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3148</v>
+        <v>244</v>
       </c>
       <c r="C2" t="n">
-        <v>9457</v>
+        <v>9151</v>
       </c>
       <c r="D2" t="n">
-        <v>12644</v>
+        <v>11788</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1950</v>
+        <v>272</v>
       </c>
       <c r="C3" t="n">
-        <v>4110</v>
+        <v>2602</v>
       </c>
       <c r="D3" t="n">
-        <v>10584</v>
+        <v>10078</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2070</v>
+        <v>346</v>
       </c>
       <c r="C4" t="n">
-        <v>4844</v>
+        <v>2898</v>
       </c>
       <c r="D4" t="n">
-        <v>9697</v>
+        <v>9695</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1993</v>
+        <v>427</v>
       </c>
       <c r="C5" t="n">
-        <v>6896</v>
+        <v>4308</v>
       </c>
       <c r="D5" t="n">
-        <v>5457</v>
+        <v>5986</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1390</v>
+        <v>336</v>
       </c>
       <c r="C6" t="n">
-        <v>8225</v>
+        <v>5714</v>
       </c>
       <c r="D6" t="n">
-        <v>2136</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>490</v>
+        <v>152</v>
       </c>
       <c r="C7" t="n">
-        <v>6352</v>
+        <v>5493</v>
       </c>
       <c r="D7" t="n">
-        <v>829</v>
+        <v>963</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="C8" t="n">
-        <v>3354</v>
+        <v>3248</v>
       </c>
       <c r="D8" t="n">
-        <v>447</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>1192</v>
+        <v>1219</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4039</v>
+        <v>1431</v>
       </c>
       <c r="C2" t="n">
-        <v>4445</v>
+        <v>20199</v>
       </c>
       <c r="D2" t="n">
-        <v>5566</v>
+        <v>16351</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2250</v>
+        <v>477</v>
       </c>
       <c r="C2" t="n">
-        <v>5447</v>
+        <v>11444</v>
       </c>
       <c r="D2" t="n">
-        <v>9305</v>
+        <v>15211</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2608</v>
+        <v>217</v>
       </c>
       <c r="C3" t="n">
-        <v>5669</v>
+        <v>4812</v>
       </c>
       <c r="D3" t="n">
-        <v>11621</v>
+        <v>9635</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2879</v>
+        <v>272</v>
       </c>
       <c r="C4" t="n">
-        <v>7229</v>
+        <v>2673</v>
       </c>
       <c r="D4" t="n">
-        <v>9967</v>
+        <v>9366</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1339</v>
+        <v>363</v>
       </c>
       <c r="C5" t="n">
-        <v>10883</v>
+        <v>3582</v>
       </c>
       <c r="D5" t="n">
-        <v>4975</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>452</v>
+        <v>344</v>
       </c>
       <c r="C6" t="n">
-        <v>7837</v>
+        <v>5052</v>
       </c>
       <c r="D6" t="n">
-        <v>1753</v>
+        <v>3099</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>204</v>
       </c>
       <c r="C7" t="n">
-        <v>3286</v>
+        <v>5530</v>
       </c>
       <c r="D7" t="n">
-        <v>543</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>1168</v>
+        <v>4170</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>2001</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>689</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D13" t="n">
         <v>38</v>
-      </c>
-      <c r="D13" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6068</v>
+        <v>3373</v>
       </c>
       <c r="C2" t="n">
-        <v>7307</v>
+        <v>11520</v>
       </c>
       <c r="D2" t="n">
-        <v>11302</v>
+        <v>18266</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1718</v>
+        <v>465</v>
       </c>
       <c r="C3" t="n">
-        <v>2275</v>
+        <v>7976</v>
       </c>
       <c r="D3" t="n">
-        <v>1618</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3673</v>
+        <v>3076</v>
       </c>
       <c r="C2" t="n">
-        <v>6917</v>
+        <v>4643</v>
       </c>
       <c r="D2" t="n">
-        <v>13714</v>
+        <v>16097</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3241</v>
+        <v>1639</v>
       </c>
       <c r="C3" t="n">
-        <v>4454</v>
+        <v>8654</v>
       </c>
       <c r="D3" t="n">
-        <v>3125</v>
+        <v>5341</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>780</v>
+        <v>243</v>
       </c>
       <c r="C4" t="n">
-        <v>1397</v>
+        <v>4949</v>
       </c>
       <c r="D4" t="n">
-        <v>1507</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>136</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5120</v>
+        <v>1814</v>
       </c>
       <c r="C2" t="n">
-        <v>7605</v>
+        <v>4363</v>
       </c>
       <c r="D2" t="n">
-        <v>22803</v>
+        <v>21003</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2849</v>
+        <v>1939</v>
       </c>
       <c r="C3" t="n">
-        <v>5073</v>
+        <v>5542</v>
       </c>
       <c r="D3" t="n">
-        <v>4594</v>
+        <v>6754</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1726</v>
+        <v>817</v>
       </c>
       <c r="C4" t="n">
-        <v>3086</v>
+        <v>7015</v>
       </c>
       <c r="D4" t="n">
-        <v>1757</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>381</v>
+        <v>149</v>
       </c>
       <c r="C5" t="n">
-        <v>870</v>
+        <v>2887</v>
       </c>
       <c r="D5" t="n">
-        <v>1211</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5765</v>
+        <v>1811</v>
       </c>
       <c r="C2" t="n">
-        <v>5890</v>
+        <v>3245</v>
       </c>
       <c r="D2" t="n">
-        <v>21279</v>
+        <v>19775</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3211</v>
+        <v>1570</v>
       </c>
       <c r="C3" t="n">
-        <v>5562</v>
+        <v>4258</v>
       </c>
       <c r="D3" t="n">
-        <v>7038</v>
+        <v>8547</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1934</v>
+        <v>1161</v>
       </c>
       <c r="C4" t="n">
-        <v>4109</v>
+        <v>6048</v>
       </c>
       <c r="D4" t="n">
-        <v>2204</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>873</v>
+        <v>402</v>
       </c>
       <c r="C5" t="n">
-        <v>2021</v>
+        <v>5046</v>
       </c>
       <c r="D5" t="n">
-        <v>1273</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>231</v>
+        <v>119</v>
       </c>
       <c r="C6" t="n">
-        <v>585</v>
+        <v>1617</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>827</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6654</v>
+        <v>1462</v>
       </c>
       <c r="C2" t="n">
-        <v>8992</v>
+        <v>6779</v>
       </c>
       <c r="D2" t="n">
-        <v>22757</v>
+        <v>31735</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3252</v>
+        <v>1388</v>
       </c>
       <c r="C3" t="n">
-        <v>4692</v>
+        <v>3267</v>
       </c>
       <c r="D3" t="n">
-        <v>8191</v>
+        <v>9651</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1607</v>
+        <v>1169</v>
       </c>
       <c r="C4" t="n">
-        <v>4038</v>
+        <v>4977</v>
       </c>
       <c r="D4" t="n">
-        <v>2616</v>
+        <v>4035</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>732</v>
+        <v>646</v>
       </c>
       <c r="C5" t="n">
-        <v>2272</v>
+        <v>5450</v>
       </c>
       <c r="D5" t="n">
-        <v>1138</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>262</v>
+        <v>224</v>
       </c>
       <c r="C6" t="n">
-        <v>891</v>
+        <v>3262</v>
       </c>
       <c r="D6" t="n">
-        <v>757</v>
+        <v>889</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C7" t="n">
-        <v>300</v>
+        <v>942</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4592</v>
+        <v>1083</v>
       </c>
       <c r="C2" t="n">
-        <v>10664</v>
+        <v>11399</v>
       </c>
       <c r="D2" t="n">
-        <v>19320</v>
+        <v>31033</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4149</v>
+        <v>1176</v>
       </c>
       <c r="C3" t="n">
-        <v>6225</v>
+        <v>4302</v>
       </c>
       <c r="D3" t="n">
-        <v>10138</v>
+        <v>12005</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2153</v>
+        <v>1096</v>
       </c>
       <c r="C4" t="n">
-        <v>4355</v>
+        <v>3988</v>
       </c>
       <c r="D4" t="n">
-        <v>3713</v>
+        <v>4790</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1050</v>
+        <v>766</v>
       </c>
       <c r="C5" t="n">
-        <v>3254</v>
+        <v>5109</v>
       </c>
       <c r="D5" t="n">
-        <v>1401</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>461</v>
+        <v>367</v>
       </c>
       <c r="C6" t="n">
-        <v>1688</v>
+        <v>4237</v>
       </c>
       <c r="D6" t="n">
-        <v>811</v>
+        <v>978</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>641</v>
+        <v>1978</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>265</v>
+        <v>583</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3280</v>
+        <v>1066</v>
       </c>
       <c r="C2" t="n">
-        <v>12110</v>
+        <v>7204</v>
       </c>
       <c r="D2" t="n">
-        <v>24260</v>
+        <v>24560</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3604</v>
+        <v>1735</v>
       </c>
       <c r="C3" t="n">
-        <v>7509</v>
+        <v>7461</v>
       </c>
       <c r="D3" t="n">
-        <v>10877</v>
+        <v>13170</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2721</v>
+        <v>707</v>
       </c>
       <c r="C4" t="n">
-        <v>5341</v>
+        <v>7316</v>
       </c>
       <c r="D4" t="n">
-        <v>4798</v>
+        <v>4529</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1394</v>
+        <v>339</v>
       </c>
       <c r="C5" t="n">
-        <v>3799</v>
+        <v>4152</v>
       </c>
       <c r="D5" t="n">
-        <v>1802</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>690</v>
+        <v>128</v>
       </c>
       <c r="C6" t="n">
-        <v>2493</v>
+        <v>1938</v>
       </c>
       <c r="D6" t="n">
-        <v>907</v>
+        <v>640</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>273</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>1205</v>
+        <v>571</v>
       </c>
       <c r="D7" t="n">
-        <v>593</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>460</v>
+        <v>279</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
